--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07CDB364-20D3-49D4-A88D-4FAF1BA0DFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBD60ECA-89C4-4495-ADA4-FCA85F30CC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -911,10 +911,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,WaD,RaP,FaD,WaP,FaP,SaP,SaD</t>
+    <t>FaD,WaD,RaD,RaP,SaD,FaP,SaP,WaP</t>
   </si>
   <si>
-    <t>WaP,SaN,WaN,RaP,RaN,FaN,FaP,SaP</t>
+    <t>SaN,WaN,RaP,FaP,SaP,FaN,WaP,RaN</t>
   </si>
 </sst>
 </file>
@@ -24570,7 +24570,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED033AB-A68F-47C5-8AA8-011A0BA1328F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18182C3D-6718-4980-9DE9-D51EE2A26D08}">
   <dimension ref="A9:AN54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24858,7 +24858,7 @@
         <v>151</v>
       </c>
       <c r="AM12">
-        <v>0.30699614484801707</v>
+        <v>0.30699614484801702</v>
       </c>
       <c r="AN12" t="s">
         <v>270</v>
@@ -25058,7 +25058,7 @@
         <v>151</v>
       </c>
       <c r="AM16">
-        <v>0.24156666666666668</v>
+        <v>0.24156666666666671</v>
       </c>
       <c r="AN16" t="s">
         <v>270</v>
@@ -25108,7 +25108,7 @@
         <v>151</v>
       </c>
       <c r="AM17">
-        <v>0.24865000000000001</v>
+        <v>0.24865000000000004</v>
       </c>
       <c r="AN17" t="s">
         <v>270</v>
@@ -25208,7 +25208,7 @@
         <v>151</v>
       </c>
       <c r="AM19">
-        <v>0.29982500000000001</v>
+        <v>0.29982499999999995</v>
       </c>
       <c r="AN19" t="s">
         <v>270</v>
@@ -25308,7 +25308,7 @@
         <v>151</v>
       </c>
       <c r="AM21">
-        <v>0.29033333333333333</v>
+        <v>0.29033333333333328</v>
       </c>
       <c r="AN21" t="s">
         <v>270</v>
@@ -25408,7 +25408,7 @@
         <v>151</v>
       </c>
       <c r="AM23">
-        <v>0.29926666666666663</v>
+        <v>0.29926666666666668</v>
       </c>
       <c r="AN23" t="s">
         <v>270</v>
@@ -25658,7 +25658,7 @@
         <v>151</v>
       </c>
       <c r="AM28">
-        <v>0.33744166666666664</v>
+        <v>0.3374416666666667</v>
       </c>
       <c r="AN28" t="s">
         <v>270</v>
@@ -26208,7 +26208,7 @@
         <v>151</v>
       </c>
       <c r="AM39">
-        <v>0.29419999999999996</v>
+        <v>0.29420000000000002</v>
       </c>
       <c r="AN39" t="s">
         <v>270</v>
@@ -26478,7 +26478,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0326032-D7AC-4515-AC30-706AA7C54868}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF248ECA-3D00-453C-BB8E-E3AABBA23380}">
   <dimension ref="A9:AN538"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26707,7 +26707,7 @@
         <v>271</v>
       </c>
       <c r="AM11">
-        <v>0.23974469689443209</v>
+        <v>0.23974469689443212</v>
       </c>
       <c r="AN11" t="s">
         <v>270</v>
@@ -27208,7 +27208,7 @@
         <v>274</v>
       </c>
       <c r="AM17">
-        <v>0.38272369981898208</v>
+        <v>0.38272369981898219</v>
       </c>
       <c r="AN17" t="s">
         <v>270</v>
@@ -27448,7 +27448,7 @@
         <v>273</v>
       </c>
       <c r="AM20">
-        <v>0.33776913495513355</v>
+        <v>0.33776913495513367</v>
       </c>
       <c r="AN20" t="s">
         <v>270</v>
@@ -27528,7 +27528,7 @@
         <v>274</v>
       </c>
       <c r="AM21">
-        <v>0.34928230678631045</v>
+        <v>0.34928230678631039</v>
       </c>
       <c r="AN21" t="s">
         <v>270</v>
@@ -27726,7 +27726,7 @@
         <v>273</v>
       </c>
       <c r="AM24">
-        <v>0.27543333333333331</v>
+        <v>0.27543333333333336</v>
       </c>
       <c r="AN24" t="s">
         <v>270</v>
@@ -27785,7 +27785,7 @@
         <v>274</v>
       </c>
       <c r="AM25">
-        <v>0.29716666666666663</v>
+        <v>0.29716666666666669</v>
       </c>
       <c r="AN25" t="s">
         <v>270</v>
@@ -28021,7 +28021,7 @@
         <v>274</v>
       </c>
       <c r="AM29">
-        <v>0.30223333333333335</v>
+        <v>0.3022333333333333</v>
       </c>
       <c r="AN29" t="s">
         <v>270</v>
@@ -28257,7 +28257,7 @@
         <v>274</v>
       </c>
       <c r="AM33">
-        <v>0.28860000000000002</v>
+        <v>0.28859999999999997</v>
       </c>
       <c r="AN33" t="s">
         <v>270</v>
@@ -28416,7 +28416,7 @@
         <v>273</v>
       </c>
       <c r="AM36">
-        <v>0.29613333333333336</v>
+        <v>0.2961333333333333</v>
       </c>
       <c r="AN36" t="s">
         <v>270</v>
@@ -28616,7 +28616,7 @@
         <v>273</v>
       </c>
       <c r="AM40">
-        <v>0.35266666666666668</v>
+        <v>0.35266666666666663</v>
       </c>
       <c r="AN40" t="s">
         <v>270</v>
@@ -29066,7 +29066,7 @@
         <v>274</v>
       </c>
       <c r="AM49">
-        <v>0.35790000000000005</v>
+        <v>0.35789999999999994</v>
       </c>
       <c r="AN49" t="s">
         <v>270</v>
@@ -29666,7 +29666,7 @@
         <v>274</v>
       </c>
       <c r="AM61">
-        <v>0.37543333333333334</v>
+        <v>0.37543333333333329</v>
       </c>
       <c r="AN61" t="s">
         <v>270</v>
@@ -29766,7 +29766,7 @@
         <v>271</v>
       </c>
       <c r="AM63">
-        <v>0.24509999999999998</v>
+        <v>0.24510000000000001</v>
       </c>
       <c r="AN63" t="s">
         <v>270</v>
@@ -30066,7 +30066,7 @@
         <v>274</v>
       </c>
       <c r="AM69">
-        <v>0.35840000000000005</v>
+        <v>0.3584</v>
       </c>
       <c r="AN69" t="s">
         <v>270</v>
@@ -30266,7 +30266,7 @@
         <v>274</v>
       </c>
       <c r="AM73">
-        <v>0.36189999999999994</v>
+        <v>0.36190000000000005</v>
       </c>
       <c r="AN73" t="s">
         <v>270</v>
@@ -30666,7 +30666,7 @@
         <v>274</v>
       </c>
       <c r="AM81">
-        <v>0.40093333333333331</v>
+        <v>0.40093333333333336</v>
       </c>
       <c r="AN81" t="s">
         <v>270</v>
@@ -31366,7 +31366,7 @@
         <v>271</v>
       </c>
       <c r="AM95">
-        <v>0.2906333333333333</v>
+        <v>0.29063333333333335</v>
       </c>
       <c r="AN95" t="s">
         <v>270</v>
@@ -31566,7 +31566,7 @@
         <v>271</v>
       </c>
       <c r="AM99">
-        <v>0.24106666666666668</v>
+        <v>0.24106666666666665</v>
       </c>
       <c r="AN99" t="s">
         <v>270</v>
@@ -32166,7 +32166,7 @@
         <v>271</v>
       </c>
       <c r="AM111">
-        <v>0.25489999999999996</v>
+        <v>0.25490000000000002</v>
       </c>
       <c r="AN111" t="s">
         <v>270</v>
@@ -32666,7 +32666,7 @@
         <v>274</v>
       </c>
       <c r="AM121">
-        <v>0.35863333333333336</v>
+        <v>0.3586333333333333</v>
       </c>
       <c r="AN121" t="s">
         <v>270</v>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBD60ECA-89C4-4495-ADA4-FCA85F30CC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE7BB442-C27E-444F-B213-6E3C24E2CCCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -911,10 +911,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaD,WaD,RaD,RaP,SaD,FaP,SaP,WaP</t>
+    <t>WaD,RaD,FaP,SaP,RaP,SaD,FaD,WaP</t>
   </si>
   <si>
-    <t>SaN,WaN,RaP,FaP,SaP,FaN,WaP,RaN</t>
+    <t>FaN,FaP,SaP,RaP,SaN,WaN,RaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24570,7 +24570,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18182C3D-6718-4980-9DE9-D51EE2A26D08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D748AF8-6F6F-4C06-8576-56D1F2EBD4D5}">
   <dimension ref="A9:AN54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24799,7 +24799,7 @@
         <v>151</v>
       </c>
       <c r="AM11">
-        <v>0.30535401969734755</v>
+        <v>0.3053540196973476</v>
       </c>
       <c r="AN11" t="s">
         <v>270</v>
@@ -25108,7 +25108,7 @@
         <v>151</v>
       </c>
       <c r="AM17">
-        <v>0.24865000000000004</v>
+        <v>0.24865000000000001</v>
       </c>
       <c r="AN17" t="s">
         <v>270</v>
@@ -25208,7 +25208,7 @@
         <v>151</v>
       </c>
       <c r="AM19">
-        <v>0.29982499999999995</v>
+        <v>0.29982500000000001</v>
       </c>
       <c r="AN19" t="s">
         <v>270</v>
@@ -25308,7 +25308,7 @@
         <v>151</v>
       </c>
       <c r="AM21">
-        <v>0.29033333333333328</v>
+        <v>0.29033333333333333</v>
       </c>
       <c r="AN21" t="s">
         <v>270</v>
@@ -25408,7 +25408,7 @@
         <v>151</v>
       </c>
       <c r="AM23">
-        <v>0.29926666666666668</v>
+        <v>0.29926666666666663</v>
       </c>
       <c r="AN23" t="s">
         <v>270</v>
@@ -25608,7 +25608,7 @@
         <v>151</v>
       </c>
       <c r="AM27">
-        <v>0.29666666666666669</v>
+        <v>0.29666666666666663</v>
       </c>
       <c r="AN27" t="s">
         <v>270</v>
@@ -25808,7 +25808,7 @@
         <v>151</v>
       </c>
       <c r="AM31">
-        <v>0.3399833333333333</v>
+        <v>0.33998333333333336</v>
       </c>
       <c r="AN31" t="s">
         <v>270</v>
@@ -26158,7 +26158,7 @@
         <v>151</v>
       </c>
       <c r="AM38">
-        <v>0.29490833333333327</v>
+        <v>0.29490833333333333</v>
       </c>
       <c r="AN38" t="s">
         <v>270</v>
@@ -26478,7 +26478,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF248ECA-3D00-453C-BB8E-E3AABBA23380}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5922BE4-1857-4902-8C43-56187265D9CD}">
   <dimension ref="A9:AN538"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26707,7 +26707,7 @@
         <v>271</v>
       </c>
       <c r="AM11">
-        <v>0.23974469689443212</v>
+        <v>0.23974469689443209</v>
       </c>
       <c r="AN11" t="s">
         <v>270</v>
@@ -27128,7 +27128,7 @@
         <v>273</v>
       </c>
       <c r="AM16">
-        <v>0.37560454384911296</v>
+        <v>0.3756045438491129</v>
       </c>
       <c r="AN16" t="s">
         <v>270</v>
@@ -27448,7 +27448,7 @@
         <v>273</v>
       </c>
       <c r="AM20">
-        <v>0.33776913495513367</v>
+        <v>0.33776913495513355</v>
       </c>
       <c r="AN20" t="s">
         <v>270</v>
@@ -27785,7 +27785,7 @@
         <v>274</v>
       </c>
       <c r="AM25">
-        <v>0.29716666666666669</v>
+        <v>0.29716666666666663</v>
       </c>
       <c r="AN25" t="s">
         <v>270</v>
@@ -28416,7 +28416,7 @@
         <v>273</v>
       </c>
       <c r="AM36">
-        <v>0.2961333333333333</v>
+        <v>0.29613333333333336</v>
       </c>
       <c r="AN36" t="s">
         <v>270</v>
@@ -28816,7 +28816,7 @@
         <v>273</v>
       </c>
       <c r="AM44">
-        <v>0.35719999999999996</v>
+        <v>0.35720000000000002</v>
       </c>
       <c r="AN44" t="s">
         <v>270</v>
@@ -29066,7 +29066,7 @@
         <v>274</v>
       </c>
       <c r="AM49">
-        <v>0.35789999999999994</v>
+        <v>0.35790000000000005</v>
       </c>
       <c r="AN49" t="s">
         <v>270</v>
@@ -29666,7 +29666,7 @@
         <v>274</v>
       </c>
       <c r="AM61">
-        <v>0.37543333333333329</v>
+        <v>0.37543333333333334</v>
       </c>
       <c r="AN61" t="s">
         <v>270</v>
@@ -29766,7 +29766,7 @@
         <v>271</v>
       </c>
       <c r="AM63">
-        <v>0.24510000000000001</v>
+        <v>0.24509999999999998</v>
       </c>
       <c r="AN63" t="s">
         <v>270</v>
@@ -30466,7 +30466,7 @@
         <v>274</v>
       </c>
       <c r="AM77">
-        <v>0.3741666666666667</v>
+        <v>0.37416666666666659</v>
       </c>
       <c r="AN77" t="s">
         <v>270</v>
@@ -30666,7 +30666,7 @@
         <v>274</v>
       </c>
       <c r="AM81">
-        <v>0.40093333333333336</v>
+        <v>0.40093333333333331</v>
       </c>
       <c r="AN81" t="s">
         <v>270</v>
@@ -31016,7 +31016,7 @@
         <v>273</v>
       </c>
       <c r="AM88">
-        <v>0.38750000000000001</v>
+        <v>0.38749999999999996</v>
       </c>
       <c r="AN88" t="s">
         <v>270</v>
@@ -31366,7 +31366,7 @@
         <v>271</v>
       </c>
       <c r="AM95">
-        <v>0.29063333333333335</v>
+        <v>0.2906333333333333</v>
       </c>
       <c r="AN95" t="s">
         <v>270</v>
@@ -31566,7 +31566,7 @@
         <v>271</v>
       </c>
       <c r="AM99">
-        <v>0.24106666666666665</v>
+        <v>0.24106666666666668</v>
       </c>
       <c r="AN99" t="s">
         <v>270</v>
@@ -32166,7 +32166,7 @@
         <v>271</v>
       </c>
       <c r="AM111">
-        <v>0.25490000000000002</v>
+        <v>0.25489999999999996</v>
       </c>
       <c r="AN111" t="s">
         <v>270</v>
@@ -32416,7 +32416,7 @@
         <v>273</v>
       </c>
       <c r="AM116">
-        <v>0.33629999999999999</v>
+        <v>0.33630000000000004</v>
       </c>
       <c r="AN116" t="s">
         <v>270</v>

--- a/VerveStacks_JPN_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_JPN_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB5E295D-2D33-4EAE-8A3B-09A5A7936C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{541E3A45-9505-4C60-AB43-03F3A0189AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -911,10 +911,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaP,RaD,SaD,FaD,WaD,FaP,SaP,WaP</t>
+    <t>WaD,WaP,FaP,SaP,RaD,FaD,SaD,RaP</t>
   </si>
   <si>
-    <t>FaN,WaP,SaN,WaN,FaP,SaP,RaP,RaN</t>
+    <t>RaN,WaP,RaP,FaP,SaP,FaN,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24570,7 +24570,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B058B11C-BEAF-47DA-8126-716EA455DEE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54E6B659-C82D-4AE1-82C6-6FDD1B1BB4FD}">
   <dimension ref="A9:AN54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24858,7 +24858,7 @@
         <v>151</v>
       </c>
       <c r="AM12">
-        <v>0.30699614484801702</v>
+        <v>0.30699614484801707</v>
       </c>
       <c r="AN12" t="s">
         <v>270</v>
@@ -24908,7 +24908,7 @@
         <v>151</v>
       </c>
       <c r="AM13">
-        <v>0.28403614521636716</v>
+        <v>0.28403614521636711</v>
       </c>
       <c r="AN13" t="s">
         <v>270</v>
@@ -25108,7 +25108,7 @@
         <v>151</v>
       </c>
       <c r="AM17">
-        <v>0.24864999999999995</v>
+        <v>0.24865000000000001</v>
       </c>
       <c r="AN17" t="s">
         <v>270</v>
@@ -25258,7 +25258,7 @@
         <v>151</v>
       </c>
       <c r="AM20">
-        <v>0.29724999999999996</v>
+        <v>0.29725000000000001</v>
       </c>
       <c r="AN20" t="s">
         <v>270</v>
@@ -25308,7 +25308,7 @@
         <v>151</v>
       </c>
       <c r="AM21">
-        <v>0.29033333333333333</v>
+        <v>0.29033333333333328</v>
       </c>
       <c r="AN21" t="s">
         <v>270</v>
@@ -25408,7 +25408,7 @@
         <v>151</v>
       </c>
       <c r="AM23">
-        <v>0.29926666666666663</v>
+        <v>0.29926666666666674</v>
       </c>
       <c r="AN23" t="s">
         <v>270</v>
@@ -25558,7 +25558,7 @@
         <v>151</v>
       </c>
       <c r="AM26">
-        <v>0.29800833333333338</v>
+        <v>0.29800833333333332</v>
       </c>
       <c r="AN26" t="s">
         <v>270</v>
@@ -25658,7 +25658,7 @@
         <v>151</v>
       </c>
       <c r="AM28">
-        <v>0.3374416666666667</v>
+        <v>0.33744166666666664</v>
       </c>
       <c r="AN28" t="s">
         <v>270</v>
@@ -25708,7 +25708,7 @@
         <v>151</v>
       </c>
       <c r="AM29">
-        <v>0.33389166666666664</v>
+        <v>0.3338916666666667</v>
       </c>
       <c r="AN29" t="s">
         <v>270</v>
@@ -26478,7 +26478,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F32FE7D8-FD51-4A6F-AC5C-1706F1D9D540}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4737982-8192-4B2B-97ED-5A1DD3454DF3}">
   <dimension ref="A9:AN538"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26707,7 +26707,7 @@
         <v>271</v>
       </c>
       <c r="AM11">
-        <v>0.23974469689443212</v>
+        <v>0.23974469689443209</v>
       </c>
       <c r="AN11" t="s">
         <v>270</v>
@@ -27128,7 +27128,7 @@
         <v>273</v>
       </c>
       <c r="AM16">
-        <v>0.37560454384911296</v>
+        <v>0.3756045438491129</v>
       </c>
       <c r="AN16" t="s">
         <v>270</v>
@@ -27448,7 +27448,7 @@
         <v>273</v>
       </c>
       <c r="AM20">
-        <v>0.33776913495513367</v>
+        <v>0.33776913495513355</v>
       </c>
       <c r="AN20" t="s">
         <v>270</v>
@@ -28316,7 +28316,7 @@
         <v>276</v>
       </c>
       <c r="AM34">
-        <v>0.18130000000000002</v>
+        <v>0.18129999999999999</v>
       </c>
       <c r="AN34" t="s">
         <v>270</v>
@@ -28416,7 +28416,7 @@
         <v>273</v>
       </c>
       <c r="AM36">
-        <v>0.2961333333333333</v>
+        <v>0.29613333333333336</v>
       </c>
       <c r="AN36" t="s">
         <v>270</v>
@@ -28816,7 +28816,7 @@
         <v>273</v>
       </c>
       <c r="AM44">
-        <v>0.35719999999999996</v>
+        <v>0.35720000000000002</v>
       </c>
       <c r="AN44" t="s">
         <v>270</v>
@@ -28916,7 +28916,7 @@
         <v>276</v>
       </c>
       <c r="AM46">
-        <v>0.22220000000000004</v>
+        <v>0.22219999999999998</v>
       </c>
       <c r="AN46" t="s">
         <v>270</v>
@@ -29116,7 +29116,7 @@
         <v>276</v>
       </c>
       <c r="AM50">
-        <v>0.21673333333333336</v>
+        <v>0.21673333333333333</v>
       </c>
       <c r="AN50" t="s">
         <v>270</v>
@@ -29766,7 +29766,7 @@
         <v>271</v>
       </c>
       <c r="AM63">
-        <v>0.24510000000000001</v>
+        <v>0.24509999999999998</v>
       </c>
       <c r="AN63" t="s">
         <v>270</v>
@@ -29916,7 +29916,7 @@
         <v>276</v>
       </c>
       <c r="AM66">
-        <v>0.22353333333333333</v>
+        <v>0.22353333333333336</v>
       </c>
       <c r="AN66" t="s">
         <v>270</v>
@@ -30716,7 +30716,7 @@
         <v>276</v>
       </c>
       <c r="AM82">
-        <v>0.24716666666666665</v>
+        <v>0.24716666666666667</v>
       </c>
       <c r="AN82" t="s">
         <v>270</v>
@@ -30916,7 +30916,7 @@
         <v>276</v>
       </c>
       <c r="AM86">
-        <v>0.24556666666666663</v>
+        <v>0.24556666666666668</v>
       </c>
       <c r="AN86" t="s">
         <v>270</v>
@@ -31016,7 +31016,7 @@
         <v>273</v>
       </c>
       <c r="AM88">
-        <v>0.38750000000000001</v>
+        <v>0.38749999999999996</v>
       </c>
       <c r="AN88" t="s">
         <v>270</v>
@@ -31366,7 +31366,7 @@
         <v>271</v>
       </c>
       <c r="AM95">
-        <v>0.29063333333333335</v>
+        <v>0.2906333333333333</v>
       </c>
       <c r="AN95" t="s">
         <v>270</v>
@@ -31566,7 +31566,7 @@
         <v>271</v>
       </c>
       <c r="AM99">
-        <v>0.24106666666666665</v>
+        <v>0.24106666666666668</v>
       </c>
       <c r="AN99" t="s">
         <v>270</v>
@@ -31916,7 +31916,7 @@
         <v>276</v>
       </c>
       <c r="AM106">
-        <v>0.20546666666666669</v>
+        <v>0.20546666666666666</v>
       </c>
       <c r="AN106" t="s">
         <v>270</v>
@@ -32166,7 +32166,7 @@
         <v>271</v>
       </c>
       <c r="AM111">
-        <v>0.25490000000000002</v>
+        <v>0.25489999999999996</v>
       </c>
       <c r="AN111" t="s">
         <v>270</v>
@@ -32416,7 +32416,7 @@
         <v>273</v>
       </c>
       <c r="AM116">
-        <v>0.33629999999999999</v>
+        <v>0.33630000000000004</v>
       </c>
       <c r="AN116" t="s">
         <v>270</v>
@@ -32516,7 +32516,7 @@
         <v>276</v>
       </c>
       <c r="AM118">
-        <v>0.22026666666666664</v>
+        <v>0.22026666666666669</v>
       </c>
       <c r="AN118" t="s">
         <v>270</v>
@@ -32916,7 +32916,7 @@
         <v>276</v>
       </c>
       <c r="AM126">
-        <v>0.21156666666666665</v>
+        <v>0.21156666666666668</v>
       </c>
       <c r="AN126" t="s">
         <v>270</v>
